--- a/public/templates/bulk-import-template.xlsx
+++ b/public/templates/bulk-import-template.xlsx
@@ -1,10 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="11_4E22B6AF77BEABA23143F343374451B34654107B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{016A3140-8D4B-41F7-9729-21A6DFC94B44}"/>
+  <bookViews>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Import" state="visible" r:id="rId4"/>
+    <sheet name="Import" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
@@ -40,9 +44,6 @@
     <t>0400000000</t>
   </si>
   <si>
-    <t>student</t>
-  </si>
-  <si>
     <t>Mary-Jane</t>
   </si>
   <si>
@@ -55,23 +56,28 @@
     <t>0400000001</t>
   </si>
   <si>
-    <t>tutor</t>
+    <t>Student</t>
+  </si>
+  <si>
+    <t>Tutor</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -435,9 +441,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E201"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="18" customWidth="1"/>
     <col min="3" max="3" width="30" customWidth="1"/>
@@ -445,7 +451,7 @@
     <col min="5" max="5" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -462,7 +468,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -476,234 +482,33 @@
         <v>8</v>
       </c>
       <c r="E2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="B3" t="s">
         <v>10</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>11</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>12</v>
-      </c>
-      <c r="D3" t="s">
-        <v>13</v>
       </c>
       <c r="E3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="5" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="6" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="7" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="8" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="9" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="10" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="11" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="12" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="13" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="15" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="16" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="17" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="18" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="19" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="20" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="21" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="22" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="23" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="24" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="25" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="26" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="27" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="28" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="29" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="30" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="31" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="32" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="33" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="34" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="35" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="36" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="37" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="38" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="39" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="40" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="41" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="42" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="43" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="44" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="45" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="46" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="47" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="48" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="49" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="50" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="51" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="52" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="53" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="54" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="55" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="56" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="57" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="58" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="59" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="60" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="61" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="62" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="63" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="64" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="65" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="66" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="67" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="68" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="69" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="70" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="71" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="72" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="73" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="74" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="75" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="76" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="77" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="78" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="79" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="80" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="81" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="82" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="83" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="84" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="85" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="86" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="87" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="88" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="89" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="90" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="91" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="92" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="93" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="94" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="95" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="96" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="97" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="98" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="99" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="100" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="101" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="102" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="103" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="104" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="105" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="106" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="107" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="108" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="109" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="110" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="111" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="112" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="113" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="114" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="115" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="116" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="117" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="118" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="119" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="120" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="121" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="122" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="123" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="124" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="125" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="126" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="127" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="128" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="129" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="130" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="131" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="132" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="133" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="134" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="135" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="136" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="137" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="138" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="139" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="140" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="141" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="142" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="143" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="144" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="145" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="146" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="147" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="148" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="149" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="150" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="151" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="152" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="153" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="154" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="155" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="156" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="157" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="158" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="159" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="160" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="161" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="162" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="163" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="164" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="165" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="166" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="167" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="168" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="169" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="170" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="171" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="172" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="173" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="174" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="175" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="176" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="177" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="178" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="179" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="180" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="181" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="182" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="183" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="184" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="185" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="186" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="187" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="188" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="189" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="190" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="191" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="192" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="193" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="194" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="195" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="196" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="197" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="198" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="199" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="200" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="201" spans="5:5" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="error" errorTitle="Invalid role" error="Role must be one of: client, student, tutor, coordinator, liaison" sqref="E10:E201">
-      <formula1>"client,student,tutor,coordinator,liaison"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="error" errorTitle="Invalid role" error="Role must be one of: client, student, tutor, coordinator, liaison" sqref="E2:E201">
-      <formula1>"client,student,tutor,coordinator,liaison"</formula1>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid role" error="Role must be one of: client, student, tutor, coordinator, liaison" sqref="E2:E1051" xr:uid="{B0264E20-8DB1-48DD-960B-B3CCC4C4CD39}">
+      <formula1>"Client,Student,Tutor,Unit Coordinator,Liaison"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
--- a/public/templates/bulk-import-template.xlsx
+++ b/public/templates/bulk-import-template.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="12" documentId="11_4E22B6AF77BEABA23143F343374451B34654107B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{016A3140-8D4B-41F7-9729-21A6DFC94B44}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="11_D69F3177706D7D87E743F36727ECBC2F22D0338F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{407AB83F-9BDA-4E13-868F-72C5E942061A}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="14">
   <si>
     <t>firstName</t>
   </si>
@@ -41,7 +41,7 @@
     <t>jane.smith@example.com</t>
   </si>
   <si>
-    <t>0400000000</t>
+    <t>Student</t>
   </si>
   <si>
     <t>Mary-Jane</t>
@@ -53,13 +53,10 @@
     <t>mary-jane.doe@example.com</t>
   </si>
   <si>
-    <t>0400000001</t>
-  </si>
-  <si>
-    <t>Student</t>
-  </si>
-  <si>
     <t>Tutor</t>
+  </si>
+  <si>
+    <t>0412345678</t>
   </si>
 </sst>
 </file>
@@ -100,9 +97,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -118,6 +117,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -442,33 +445,33 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:E23"/>
+  <sheetFormatPr defaultRowHeight="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="18" customWidth="1"/>
     <col min="3" max="3" width="30" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="4" max="4" width="16" style="1" customWidth="1"/>
     <col min="5" max="5" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -478,14 +481,14 @@
       <c r="C2" t="s">
         <v>7</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" t="s">
         <v>8</v>
       </c>
-      <c r="E2" t="s">
-        <v>13</v>
-      </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -495,20 +498,43 @@
       <c r="C3" t="s">
         <v>11</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" t="s">
         <v>12</v>
       </c>
-      <c r="E3" t="s">
-        <v>14</v>
-      </c>
     </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25"/>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25"/>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25"/>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25"/>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25"/>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25"/>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25"/>
+    <row r="17" x14ac:dyDescent="0.25"/>
+    <row r="18" x14ac:dyDescent="0.25"/>
+    <row r="19" x14ac:dyDescent="0.25"/>
+    <row r="20" x14ac:dyDescent="0.25"/>
+    <row r="21" x14ac:dyDescent="0.25"/>
+    <row r="22" x14ac:dyDescent="0.25"/>
+    <row r="23" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid role" error="Role must be one of: client, student, tutor, coordinator, liaison" sqref="E2:E1051" xr:uid="{B0264E20-8DB1-48DD-960B-B3CCC4C4CD39}">
+  <dataValidations count="2">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="Invalid phone number" error="Phone number must be in the format 0400000000 (starts with 0, 10 digits total)." sqref="D2:D201" xr:uid="{00000000-0002-0000-0000-000000000000}">
+      <formula1>AND(LEN(D2)=10,LEFT(D2,1)="0",ISNUMBER(VALUE(MID(D2,2,9))))</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid role" error="Role must be one of: client, student, tutor, coordinator, liaison" sqref="E2:E1051" xr:uid="{00000000-0002-0000-0000-0000C8000000}">
       <formula1>"Client,Student,Tutor,Unit Coordinator,Liaison"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>